--- a/examples/集团统计_Q2.xlsx
+++ b/examples/集团统计_Q2.xlsx
@@ -911,7 +911,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-12 01:40:45</t>
+          <t>2026-06-12 02:01:52</t>
         </is>
       </c>
     </row>

--- a/examples/集团统计_Q2.xlsx
+++ b/examples/集团统计_Q2.xlsx
@@ -911,7 +911,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-12 02:01:52</t>
+          <t>2026-06-12 02:33:30</t>
         </is>
       </c>
     </row>

--- a/examples/集团统计_Q2.xlsx
+++ b/examples/集团统计_Q2.xlsx
@@ -911,7 +911,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-12 02:33:30</t>
+          <t>2026-06-12 02:43:57</t>
         </is>
       </c>
     </row>
